--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -138,6 +138,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -654,7 +660,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -678,7 +684,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -702,7 +708,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -726,7 +732,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -750,7 +756,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -774,7 +780,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -798,7 +804,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -822,7 +828,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -846,7 +852,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -870,7 +876,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -894,7 +900,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -918,7 +924,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -942,7 +948,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -966,7 +972,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -990,7 +996,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1014,7 +1020,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1038,7 +1044,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1062,7 +1068,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1086,7 +1092,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1094,18 +1100,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="15">
+      <c r="E34" s="17">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="17">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1114,7 +1120,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -1122,7 +1128,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1131,11 +1137,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="15">
+      <c r="F37" s="17">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1302,7 +1308,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1326,7 +1332,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1350,7 +1356,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1374,7 +1380,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1398,7 +1404,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1422,7 +1428,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1446,7 +1452,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1470,7 +1476,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1494,7 +1500,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1518,7 +1524,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1542,7 +1548,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1566,7 +1572,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1590,7 +1596,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1614,7 +1620,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1638,7 +1644,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1662,7 +1668,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1686,7 +1692,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1710,7 +1716,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1734,7 +1740,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1758,7 +1764,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1766,18 +1772,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1786,7 +1792,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1794,7 +1800,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1803,11 +1809,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1972,7 +1978,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1996,7 +2002,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2020,7 +2026,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2044,7 +2050,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2068,7 +2074,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2092,7 +2098,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2116,7 +2122,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2140,7 +2146,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2164,7 +2170,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2188,7 +2194,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2212,7 +2218,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2236,7 +2242,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2260,7 +2266,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2284,7 +2290,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2308,7 +2314,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2332,7 +2338,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2356,7 +2362,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2380,7 +2386,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2404,7 +2410,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2428,7 +2434,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2436,18 +2442,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2456,7 +2462,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2464,7 +2470,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2473,11 +2479,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2504,7 +2510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -2563,10 +2569,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2577,15 +2579,11 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Classroom – 350 sft (33 sqm)
-Workshop/ lab – 800 sft (75 sqm)
+lab size – 500 sft (47 sqm)
 OR
-Classroom cum workshop – 1000 sft (93 sqm)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+Classroom cum workshop – 500 sft (47 sqm)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2644,7 +2642,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2668,7 +2666,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2692,7 +2690,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2716,7 +2714,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2740,7 +2738,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2764,12 +2762,13 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Tools: Office application, photo editing software and video editing software</t>
+          <t>Tools: 
+Office application, photo editing software and video editing software, SEO Tools, Social Media Management, Email Marketing, Content Creation, CRM, Data Entry, Affiliate Marketing, bid for job, ad campaigns</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -2788,7 +2787,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2812,12 +2811,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Internet connectivity with power back-up</t>
+          <t>Internet connectivity (Minimum 10 Mbps) with power back-up (at least 01 hour)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -2836,7 +2835,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2844,18 +2843,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="15">
+      <c r="E24" s="19">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="19">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2864,7 +2863,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="15">
+      <c r="F25" s="19">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -2872,7 +2871,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2881,18 +2880,25 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="15">
+      <c r="F27" s="19">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
@@ -2901,6 +2907,7 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2971,10 +2978,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2984,13 +2987,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+          <t>Classroom – 350 sft (33 sqm)
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3049,12 +3051,13 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5-i3 6 gen or AMD Ryzen 5), Ram: minimum 8 - 16 GB, Graphic Card: dedicated GPU 2GB, High Speed Internet (Minimum 10 Mbps), Graphic Design Software (Photoshop CC, Illustrator CC, CorelDraw)</t>
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+(Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -3073,7 +3076,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3097,7 +3100,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3121,7 +3124,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3145,7 +3148,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3169,7 +3172,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3193,7 +3196,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3217,16 +3220,16 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Air-conditioning (suited with workshop lab size)</t>
+          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -3240,96 +3243,80 @@
       </c>
       <c r="G23" s="9" t="n"/>
     </row>
-    <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="9">
-        <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9" t="n"/>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="19">
+        <f>SUM(E16:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>SUM(F16:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Sum</t>
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
         </is>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="15">
-        <f>SUM(E16:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>SUM(F16:F24)</f>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="19">
+        <f>F24/E24*100</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Score out of 100</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="15">
-        <f>F25/E25*100</f>
-        <v/>
-      </c>
-      <c r="G26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="9.75" customHeight="1"/>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="26" ht="9.75" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="15">
-        <f>F26*30/100</f>
-        <v/>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="19">
+        <f>F25*30/100</f>
+        <v/>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3480,7 +3467,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3504,7 +3491,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3528,7 +3515,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3552,7 +3539,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3576,7 +3563,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3600,7 +3587,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3624,7 +3611,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3648,7 +3635,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3672,7 +3659,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3696,7 +3683,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3720,7 +3707,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3744,7 +3731,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3768,7 +3755,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3792,7 +3779,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3816,7 +3803,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3840,7 +3827,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3864,7 +3851,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3888,7 +3875,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3912,7 +3899,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3920,18 +3907,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="15">
+      <c r="E34" s="17">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="17">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3940,7 +3927,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -3948,7 +3935,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3957,11 +3944,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="15">
+      <c r="F37" s="17">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4047,6 +4034,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4062,6 +4053,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">

--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -660,7 +660,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -684,7 +684,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -708,7 +708,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -732,7 +732,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -756,7 +756,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -780,7 +780,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -804,7 +804,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -828,7 +828,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -852,7 +852,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -876,7 +876,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -900,7 +900,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -924,7 +924,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -948,7 +948,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -972,7 +972,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -996,7 +996,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1020,7 +1020,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1044,7 +1044,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1068,7 +1068,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1092,7 +1092,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1100,18 +1100,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="19">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1120,7 +1120,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1137,11 +1137,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="17">
+      <c r="F37" s="19">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1308,7 +1308,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1380,7 +1380,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1476,7 +1476,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1572,7 +1572,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1596,7 +1596,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1620,7 +1620,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1644,7 +1644,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1668,7 +1668,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1692,7 +1692,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1716,7 +1716,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1740,7 +1740,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1764,7 +1764,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1772,18 +1772,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1792,7 +1792,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1809,11 +1809,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1978,7 +1978,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2002,7 +2002,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2026,7 +2026,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2050,7 +2050,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2074,7 +2074,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2098,7 +2098,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2170,7 +2170,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2194,7 +2194,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2218,7 +2218,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2242,7 +2242,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2266,7 +2266,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2290,7 +2290,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2314,7 +2314,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2362,7 +2362,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2386,7 +2386,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2410,7 +2410,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2442,18 +2442,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2462,7 +2462,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2479,11 +2479,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2529,6 +2529,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2551,6 +2552,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2569,6 +2571,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2584,7 +2590,13 @@
 Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
-    </row>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2592,6 +2604,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2603,6 +2616,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2719,7 +2733,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop: (Minimum Intel Core i5 processor (8th Gen), 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+          <t>Computers/Laptop: (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -2978,6 +2992,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2993,6 +3011,10 @@
 Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3467,7 +3489,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3491,7 +3513,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3515,7 +3537,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3539,7 +3561,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3563,7 +3585,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3587,7 +3609,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3611,7 +3633,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3635,7 +3657,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3659,7 +3681,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3683,7 +3705,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3707,7 +3729,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3731,7 +3753,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3755,7 +3777,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3779,7 +3801,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3803,7 +3825,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3827,7 +3849,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3851,7 +3873,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3875,7 +3897,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3899,7 +3921,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3907,18 +3929,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="19">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3927,7 +3949,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -3935,7 +3957,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3944,11 +3966,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="17">
+      <c r="F37" s="19">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4115,7 +4137,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4139,7 +4161,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4163,7 +4185,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4187,7 +4209,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4211,7 +4233,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4235,7 +4257,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4259,7 +4281,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4283,7 +4305,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4307,7 +4329,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4331,7 +4353,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4355,7 +4377,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4379,7 +4401,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4403,7 +4425,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4427,7 +4449,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4451,7 +4473,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4475,7 +4497,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4499,7 +4521,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4523,7 +4545,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4547,7 +4569,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4571,7 +4593,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4579,18 +4601,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4599,7 +4621,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -4607,7 +4629,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4616,11 +4638,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -2529,7 +2529,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2551,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2595,8 +2593,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2604,7 +2600,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2616,7 +2611,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2952,6 +2946,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2974,6 +2969,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -3016,6 +3012,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -3023,6 +3021,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -3034,6 +3033,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>

--- a/lab-standards/BWCCI-lab-standard.xlsx
+++ b/lab-standards/BWCCI-lab-standard.xlsx
@@ -2529,6 +2529,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2551,6 +2552,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2593,6 +2595,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2600,6 +2604,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2611,6 +2616,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop: (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+          <t>Computers/Laptop: (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -3078,7 +3084,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
